--- a/research/traditional_assets/database/data/israel/israel_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_precious_metals.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-2.635555555555555</v>
+        <v>-1.720571428571429</v>
       </c>
       <c r="H2">
-        <v>-2.635555555555555</v>
+        <v>-1.720571428571429</v>
       </c>
       <c r="I2">
-        <v>-5.235555555555555</v>
+        <v>-6.834285714285715</v>
       </c>
       <c r="J2">
-        <v>-5.235555555555555</v>
+        <v>-6.834285714285715</v>
       </c>
       <c r="K2">
-        <v>-11.308</v>
+        <v>-12.01</v>
       </c>
       <c r="L2">
-        <v>-25.12888888888889</v>
+        <v>-6.862857142857144</v>
       </c>
       <c r="M2">
-        <v>0.603</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01319474835886214</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.05332507958967103</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.603</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.803</v>
+        <v>4.155</v>
       </c>
       <c r="V2">
-        <v>0.06133479212253829</v>
+        <v>0.397227533460803</v>
       </c>
       <c r="W2">
-        <v>0.4039665772093112</v>
+        <v>-1.089448477965914</v>
       </c>
       <c r="X2">
-        <v>0.06496148417861065</v>
+        <v>0.1193163537700484</v>
       </c>
       <c r="Y2">
-        <v>0.3390050930307005</v>
+        <v>-1.208764831735962</v>
       </c>
       <c r="Z2">
-        <v>0.02740059672410643</v>
+        <v>0.2109196094974087</v>
       </c>
       <c r="AA2">
-        <v>1.38828083991303</v>
+        <v>-2.187437748645583</v>
       </c>
       <c r="AB2">
-        <v>0.06173378149812318</v>
+        <v>0.117360870399019</v>
       </c>
       <c r="AC2">
-        <v>1.326547058414907</v>
+        <v>-2.304798619044602</v>
       </c>
       <c r="AD2">
-        <v>3.125</v>
+        <v>0.333</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.125</v>
+        <v>0.333</v>
       </c>
       <c r="AG2">
-        <v>0.3220000000000001</v>
+        <v>-3.822</v>
       </c>
       <c r="AH2">
-        <v>0.06400409626216078</v>
+        <v>0.03085333086259612</v>
       </c>
       <c r="AI2">
-        <v>0.2164877034984413</v>
+        <v>0.06106730240234733</v>
       </c>
       <c r="AJ2">
-        <v>0.006996653774281865</v>
+        <v>-0.5757758360952093</v>
       </c>
       <c r="AK2">
-        <v>0.02768225584594223</v>
+        <v>-2.944530046224962</v>
       </c>
       <c r="AL2">
-        <v>0.471</v>
+        <v>0.791</v>
       </c>
       <c r="AM2">
-        <v>0.225</v>
+        <v>0.545</v>
       </c>
       <c r="AN2">
-        <v>0.4615952732644018</v>
+        <v>0.0624765478424015</v>
       </c>
       <c r="AO2">
-        <v>-5.002123142250531</v>
+        <v>-15.12010113780025</v>
       </c>
       <c r="AP2">
-        <v>0.04756277695716397</v>
+        <v>-0.7170731707317073</v>
       </c>
       <c r="AQ2">
-        <v>-10.47111111111111</v>
+        <v>-21.94495412844037</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nala Digital Commerce Ltd (TASE:NALA)</t>
+          <t>Shefa Gems Ltd (LSE:SEFA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,23 +712,8 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-1.344444444444444</v>
-      </c>
-      <c r="H3">
-        <v>-1.344444444444444</v>
-      </c>
-      <c r="I3">
-        <v>-3.244444444444444</v>
-      </c>
-      <c r="J3">
-        <v>-3.244444444444444</v>
-      </c>
       <c r="K3">
-        <v>-0.908</v>
-      </c>
-      <c r="L3">
-        <v>-2.017777777777778</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,73 +737,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.8</v>
+        <v>0.065</v>
       </c>
       <c r="V3">
-        <v>0.0909090909090909</v>
+        <v>0.01326530612244898</v>
       </c>
       <c r="W3">
-        <v>1.434439178515008</v>
+        <v>-1.246175243393602</v>
       </c>
       <c r="X3">
-        <v>0.06205931588017634</v>
+        <v>0.117501616232444</v>
       </c>
       <c r="Y3">
-        <v>1.372379862634832</v>
+        <v>-1.363676859626046</v>
       </c>
       <c r="Z3">
-        <v>-0.8720930232558139</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>2.829457364341085</v>
+        <v>-1.221436343852013</v>
       </c>
       <c r="AB3">
-        <v>0.06154944728127135</v>
+        <v>0.117501616232444</v>
       </c>
       <c r="AC3">
-        <v>2.767907917059814</v>
+        <v>-1.338937960084457</v>
       </c>
       <c r="AD3">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.325</v>
+        <v>-0.065</v>
       </c>
       <c r="AH3">
-        <v>0.01518784972022382</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.103373231773667</v>
+        <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0816505706760316</v>
+        <v>-0.01344364012409514</v>
       </c>
       <c r="AK3">
-        <v>-1.295264623955431</v>
+        <v>0.02974828375286041</v>
       </c>
       <c r="AL3">
-        <v>0.387</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>0.161</v>
+        <v>-0.243</v>
       </c>
       <c r="AN3">
-        <v>-0.3682170542635659</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-3.772609819121447</v>
+        <v>-2993.333333333333</v>
       </c>
       <c r="AP3">
-        <v>1.802325581395348</v>
+        <v>-0.008333333333333333</v>
       </c>
       <c r="AQ3">
-        <v>-9.068322981366459</v>
+        <v>36.95473251028807</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shefa Gems Ltd (LSE:SEFA)</t>
+          <t>Nala Digital Commerce Ltd (TASE:NALA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,17 +822,32 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-1.205714285714286</v>
+      </c>
+      <c r="H4">
+        <v>-1.205714285714286</v>
+      </c>
+      <c r="I4">
+        <v>-1.702857142857143</v>
+      </c>
+      <c r="J4">
+        <v>-1.702857142857143</v>
+      </c>
       <c r="K4">
-        <v>-10.4</v>
+        <v>-3.05</v>
+      </c>
+      <c r="L4">
+        <v>-1.742857142857143</v>
       </c>
       <c r="M4">
-        <v>0.603</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04046979865771812</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.05798076923076922</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -862,79 +859,76 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0.603</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0.003</v>
+        <v>4.09</v>
       </c>
       <c r="V4">
-        <v>0.0002013422818791946</v>
+        <v>0.7356115107913669</v>
       </c>
       <c r="W4">
-        <v>-0.6265060240963856</v>
+        <v>-0.9327217125382262</v>
       </c>
       <c r="X4">
-        <v>0.06786365247704497</v>
+        <v>0.1211310913076528</v>
       </c>
       <c r="Y4">
-        <v>-0.6943696765734305</v>
+        <v>-1.053852803845879</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.851851851851851</v>
       </c>
       <c r="AA4">
-        <v>-0.05289568451502449</v>
+        <v>-3.153439153439153</v>
       </c>
       <c r="AB4">
-        <v>0.06191811571497501</v>
+        <v>0.117220124565594</v>
       </c>
       <c r="AC4">
-        <v>-0.1148138002299995</v>
+        <v>-3.270659278004747</v>
       </c>
       <c r="AD4">
-        <v>2.65</v>
+        <v>0.333</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.65</v>
+        <v>0.333</v>
       </c>
       <c r="AG4">
-        <v>2.647</v>
+        <v>-3.757</v>
       </c>
       <c r="AH4">
-        <v>0.150997150997151</v>
+        <v>0.05650772102494486</v>
       </c>
       <c r="AI4">
-        <v>0.2693089430894309</v>
+        <v>0.04397200581011488</v>
       </c>
       <c r="AJ4">
-        <v>0.1508519974924488</v>
+        <v>-2.083749306711037</v>
       </c>
       <c r="AK4">
-        <v>0.2690861034868354</v>
+        <v>-1.078667815101923</v>
       </c>
       <c r="AL4">
-        <v>0.08400000000000001</v>
+        <v>0.788</v>
       </c>
       <c r="AM4">
-        <v>0.064</v>
+        <v>0.788</v>
       </c>
       <c r="AN4">
-        <v>0.3287841191066997</v>
+        <v>-0.1348178137651822</v>
       </c>
       <c r="AO4">
-        <v>-10.66666666666667</v>
+        <v>-3.781725888324873</v>
       </c>
       <c r="AP4">
-        <v>0.3284119106699752</v>
+        <v>1.521052631578947</v>
       </c>
       <c r="AQ4">
-        <v>-14</v>
+        <v>-3.781725888324873</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_precious_metals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-1.720571428571429</v>
+        <v>-2.043478260869565</v>
       </c>
       <c r="H2">
-        <v>-1.720571428571429</v>
+        <v>-2.043478260869565</v>
       </c>
       <c r="I2">
-        <v>-6.834285714285715</v>
+        <v>-2.460869565217392</v>
       </c>
       <c r="J2">
-        <v>-6.834285714285715</v>
+        <v>-2.460869565217392</v>
       </c>
       <c r="K2">
-        <v>-12.01</v>
+        <v>-2.78</v>
       </c>
       <c r="L2">
-        <v>-6.862857142857144</v>
+        <v>-2.417391304347826</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.155</v>
+        <v>2.69</v>
       </c>
       <c r="V2">
-        <v>0.397227533460803</v>
+        <v>0.2883172561629153</v>
       </c>
       <c r="W2">
-        <v>-1.089448477965914</v>
+        <v>-0.4793103448275862</v>
       </c>
       <c r="X2">
-        <v>0.1193163537700484</v>
+        <v>0.09743353174294977</v>
       </c>
       <c r="Y2">
-        <v>-1.208764831735962</v>
+        <v>-0.5767438765705359</v>
       </c>
       <c r="Z2">
-        <v>0.2109196094974087</v>
+        <v>0.5628976994615761</v>
       </c>
       <c r="AA2">
-        <v>-2.187437748645583</v>
+        <v>-1.385217816935879</v>
       </c>
       <c r="AB2">
-        <v>0.117360870399019</v>
+        <v>0.09705892459942239</v>
       </c>
       <c r="AC2">
-        <v>-2.304798619044602</v>
+        <v>-1.482276741535301</v>
       </c>
       <c r="AD2">
-        <v>0.333</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.333</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG2">
-        <v>-3.822</v>
+        <v>-2.62</v>
       </c>
       <c r="AH2">
-        <v>0.03085333086259612</v>
+        <v>0.007446808510638298</v>
       </c>
       <c r="AI2">
-        <v>0.06106730240234733</v>
+        <v>0.01832460732984293</v>
       </c>
       <c r="AJ2">
-        <v>-0.5757758360952093</v>
+        <v>-0.3904619970193741</v>
       </c>
       <c r="AK2">
-        <v>-2.944530046224962</v>
+        <v>-2.318584070796461</v>
       </c>
       <c r="AL2">
-        <v>0.791</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.545</v>
+        <v>-0.603</v>
       </c>
       <c r="AN2">
-        <v>0.0624765478424015</v>
-      </c>
-      <c r="AO2">
-        <v>-15.12010113780025</v>
+        <v>-0.03286384976525822</v>
       </c>
       <c r="AP2">
-        <v>-0.7170731707317073</v>
+        <v>1.230046948356808</v>
       </c>
       <c r="AQ2">
-        <v>-21.94495412844037</v>
+        <v>4.693200663349917</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shefa Gems Ltd (LSE:SEFA)</t>
+          <t>Iintoo Ltd (TASE:INTO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,8 +709,23 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G3">
+        <v>-2.043478260869565</v>
+      </c>
+      <c r="H3">
+        <v>-2.043478260869565</v>
+      </c>
+      <c r="I3">
+        <v>-2.460869565217392</v>
+      </c>
+      <c r="J3">
+        <v>-2.460869565217392</v>
+      </c>
       <c r="K3">
-        <v>-8.960000000000001</v>
+        <v>-2.78</v>
+      </c>
+      <c r="L3">
+        <v>-2.417391304347826</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,198 +749,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.065</v>
+        <v>2.69</v>
       </c>
       <c r="V3">
-        <v>0.01326530612244898</v>
+        <v>0.2883172561629153</v>
       </c>
       <c r="W3">
-        <v>-1.246175243393602</v>
+        <v>-0.4793103448275862</v>
       </c>
       <c r="X3">
-        <v>0.117501616232444</v>
+        <v>0.09743353174294977</v>
       </c>
       <c r="Y3">
-        <v>-1.363676859626046</v>
+        <v>-0.5767438765705359</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.5628976994615761</v>
       </c>
       <c r="AA3">
-        <v>-1.221436343852013</v>
+        <v>-1.385217816935879</v>
       </c>
       <c r="AB3">
-        <v>0.117501616232444</v>
+        <v>0.09705892459942239</v>
       </c>
       <c r="AC3">
-        <v>-1.338937960084457</v>
+        <v>-1.482276741535301</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG3">
-        <v>-0.065</v>
+        <v>-2.62</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.007446808510638298</v>
       </c>
       <c r="AI3">
-        <v>-0</v>
+        <v>0.01832460732984293</v>
       </c>
       <c r="AJ3">
-        <v>-0.01344364012409514</v>
+        <v>-0.3904619970193741</v>
       </c>
       <c r="AK3">
-        <v>0.02974828375286041</v>
+        <v>-2.318584070796461</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.243</v>
+        <v>-0.603</v>
       </c>
       <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>-2993.333333333333</v>
+        <v>-0.03286384976525822</v>
       </c>
       <c r="AP3">
-        <v>-0.008333333333333333</v>
+        <v>1.230046948356808</v>
       </c>
       <c r="AQ3">
-        <v>36.95473251028807</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nala Digital Commerce Ltd (TASE:NALA)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Precious Metals</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-1.205714285714286</v>
-      </c>
-      <c r="H4">
-        <v>-1.205714285714286</v>
-      </c>
-      <c r="I4">
-        <v>-1.702857142857143</v>
-      </c>
-      <c r="J4">
-        <v>-1.702857142857143</v>
-      </c>
-      <c r="K4">
-        <v>-3.05</v>
-      </c>
-      <c r="L4">
-        <v>-1.742857142857143</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>4.09</v>
-      </c>
-      <c r="V4">
-        <v>0.7356115107913669</v>
-      </c>
-      <c r="W4">
-        <v>-0.9327217125382262</v>
-      </c>
-      <c r="X4">
-        <v>0.1211310913076528</v>
-      </c>
-      <c r="Y4">
-        <v>-1.053852803845879</v>
-      </c>
-      <c r="Z4">
-        <v>1.851851851851851</v>
-      </c>
-      <c r="AA4">
-        <v>-3.153439153439153</v>
-      </c>
-      <c r="AB4">
-        <v>0.117220124565594</v>
-      </c>
-      <c r="AC4">
-        <v>-3.270659278004747</v>
-      </c>
-      <c r="AD4">
-        <v>0.333</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.333</v>
-      </c>
-      <c r="AG4">
-        <v>-3.757</v>
-      </c>
-      <c r="AH4">
-        <v>0.05650772102494486</v>
-      </c>
-      <c r="AI4">
-        <v>0.04397200581011488</v>
-      </c>
-      <c r="AJ4">
-        <v>-2.083749306711037</v>
-      </c>
-      <c r="AK4">
-        <v>-1.078667815101923</v>
-      </c>
-      <c r="AL4">
-        <v>0.788</v>
-      </c>
-      <c r="AM4">
-        <v>0.788</v>
-      </c>
-      <c r="AN4">
-        <v>-0.1348178137651822</v>
-      </c>
-      <c r="AO4">
-        <v>-3.781725888324873</v>
-      </c>
-      <c r="AP4">
-        <v>1.521052631578947</v>
-      </c>
-      <c r="AQ4">
-        <v>-3.781725888324873</v>
+        <v>4.693200663349917</v>
       </c>
     </row>
   </sheetData>
